--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488237_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488237_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7376</v>
+        <v>1.1725</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8405</v>
+        <v>1.3739</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1029</v>
+        <v>-0.2014</v>
       </c>
       <c r="G2" t="n">
         <v>-0.1466</v>
@@ -610,13 +610,13 @@
         <v>0.9264</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9578</v>
+        <v>0.3926</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6156</v>
+        <v>0.1489</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3422</v>
+        <v>0.2437</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ AMESTOY</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3444</v>
+        <v>1.0839</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5252</v>
+        <v>1.5303</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.1808</v>
+        <v>-0.4463</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9371</v>
+        <v>2.4553</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5314</v>
+        <v>1.8977</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4057</v>
+        <v>0.5576</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5983</v>
+        <v>3.5942</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9241</v>
+        <v>2.8986</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6742</v>
+        <v>0.6956</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6612</v>
+        <v>-1.1389</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3927</v>
+        <v>-1.001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2686</v>
+        <v>-0.138</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1853</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.778</v>
+        <v>-0.8155</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5944</v>
+        <v>-0.2111</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3724</v>
+        <v>-0.6044</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>A. FERNANDEZ AMESTOY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3323</v>
+        <v>1.0386</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4093</v>
+        <v>4.047</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.077</v>
+        <v>-3.0084</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4553</v>
+        <v>1.9371</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8977</v>
+        <v>1.5314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5576</v>
+        <v>0.4057</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5942</v>
+        <v>3.5983</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8986</v>
+        <v>2.9241</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6956</v>
+        <v>0.6742</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1389</v>
+        <v>-1.6612</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.001</v>
+        <v>-1.3927</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.138</v>
+        <v>-0.2686</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5671</v>
+        <v>-1.0838</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.332</v>
+        <v>0.1163</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2351</v>
+        <v>-1.2</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALVAREZ RICO</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0087</v>
+        <v>1.0385</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0383</v>
+        <v>2.3034</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0296</v>
+        <v>-1.2649</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7603</v>
+        <v>3.0008</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3366</v>
+        <v>3.512</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4238</v>
+        <v>-0.5112</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7096</v>
+        <v>3.9191</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2796</v>
+        <v>3.8776</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5699</v>
+        <v>0.0415</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.47</v>
+        <v>-0.9182</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6161</v>
+        <v>-0.3656</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1462</v>
+        <v>-0.5527</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1853</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.7775</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0037</v>
+        <v>0.2372</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0136</v>
+        <v>-1.0148</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5738</v>
+        <v>-0.6289</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.315</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>A. ALVAREZ RICO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5079</v>
+        <v>0.553</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6496</v>
+        <v>0.9519</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1418</v>
+        <v>-0.3989</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0008</v>
+        <v>-0.7603</v>
       </c>
       <c r="H7" t="n">
-        <v>3.512</v>
+        <v>-0.3366</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5112</v>
+        <v>-0.4238</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9191</v>
+        <v>0.7096</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8776</v>
+        <v>1.2796</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0415</v>
+        <v>-0.5699</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9182</v>
+        <v>-1.47</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3656</v>
+        <v>-1.6161</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5527</v>
+        <v>0.1462</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3082</v>
+        <v>-0.4458</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4166</v>
+        <v>-0.0901</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8915999999999999</v>
+        <v>-0.3557</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6289</v>
+        <v>1.5738</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6289</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>A. GONZALEZ PALOMO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7137</v>
+        <v>-0.4407</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5434</v>
+        <v>-0.1151</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2572</v>
+        <v>-0.3255</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0124</v>
+        <v>-1.4585</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.0592</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2841</v>
+        <v>-1.3993</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.0176</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.2668</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.2844</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0124</v>
+        <v>-1.441</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-1.326</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2841</v>
+        <v>-0.115</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2987</v>
+        <v>-0.314</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5434</v>
+        <v>-0.1324</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2447</v>
+        <v>-0.1816</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.8877</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8877</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.863</v>
+        <v>-0.6754</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.2474</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2556</v>
+        <v>-0.4279</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4258</v>
@@ -1234,13 +1234,13 @@
         <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1783</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4924</v>
+        <v>-0.1324</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3141</v>
+        <v>0.1418</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PALOMO</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9429</v>
+        <v>-0.9829</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4204</v>
+        <v>0.2496</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5225</v>
+        <v>-1.2325</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4585</v>
+        <v>-1.0124</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0592</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3993</v>
+        <v>-0.2841</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0176</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2668</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2844</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.441</v>
+        <v>-1.0124</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.326</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.115</v>
+        <v>-0.2841</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8163</v>
+        <v>0.0295</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4377</v>
+        <v>0.2496</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3785</v>
+        <v>-0.2201</v>
       </c>
       <c r="V11" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1516</v>
+        <v>-1.5821</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.465</v>
+        <v>-0.0185</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6866</v>
+        <v>-1.5635</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3947</v>
@@ -1390,13 +1390,13 @@
         <v>0.3706</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4425</v>
+        <v>-0.873</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.143</v>
+        <v>0.3034</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2995</v>
+        <v>-1.1764</v>
       </c>
       <c r="V12" t="n">
         <v>0.315</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3128</v>
+        <v>-1.6458</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2292</v>
+        <v>-1.8577</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0835</v>
+        <v>0.2119</v>
       </c>
       <c r="G13" t="n">
         <v>0.2319</v>
@@ -1468,13 +1468,13 @@
         <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0242</v>
+        <v>-0.3572</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3109</v>
+        <v>0.0606</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7133</v>
+        <v>-0.4179</v>
       </c>
       <c r="V13" t="n">
         <v>1.2589</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.4538</v>
+        <v>-3.4252</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.525</v>
+        <v>-2.8165</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9287</v>
+        <v>-0.6086</v>
       </c>
       <c r="G14" t="n">
         <v>-1.1678</v>
@@ -1546,13 +1546,13 @@
         <v>1.1117</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6183</v>
+        <v>-0.5898</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5807</v>
+        <v>0.1278</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0376</v>
+        <v>-0.7175</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.540699999999999</v>
+        <v>-2.8994</v>
       </c>
       <c r="E15" t="n">
-        <v>4.725499999999998</v>
+        <v>6.367100000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.2662</v>
+        <v>-9.265999999999998</v>
       </c>
       <c r="G15" t="n">
         <v>1.2252</v>
@@ -1624,13 +1624,13 @@
         <v>11.1171</v>
       </c>
       <c r="S15" t="n">
-        <v>-6.4665</v>
+        <v>-4.8252</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9636</v>
+        <v>0.6778000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.502800000000001</v>
+        <v>-5.5029</v>
       </c>
       <c r="V15" t="n">
         <v>4.4065</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.5633</v>
+        <v>7.155</v>
       </c>
       <c r="E16" t="n">
-        <v>7.3383</v>
+        <v>6.8486</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2251</v>
+        <v>0.3064</v>
       </c>
       <c r="G16" t="n">
         <v>2.5797</v>
@@ -1702,13 +1702,13 @@
         <v>2.4087</v>
       </c>
       <c r="S16" t="n">
-        <v>1.631</v>
+        <v>1.2227</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7236</v>
+        <v>1.2339</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0925</v>
+        <v>-0.0112</v>
       </c>
       <c r="V16" t="n">
         <v>0.9439</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.4053</v>
+        <v>5.2357</v>
       </c>
       <c r="E17" t="n">
-        <v>6.5359</v>
+        <v>6.0462</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1306</v>
+        <v>-0.8105</v>
       </c>
       <c r="G17" t="n">
         <v>3.4099</v>
@@ -1780,13 +1780,13 @@
         <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8101</v>
+        <v>1.6405</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1613</v>
+        <v>1.6716</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3512</v>
+        <v>-0.0311</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7296</v>
+        <v>1.3157</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7877999999999999</v>
+        <v>-0.3874</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9418</v>
+        <v>1.7031</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1008</v>
@@ -1858,13 +1858,13 @@
         <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>3.0342</v>
+        <v>1.6203</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4647</v>
+        <v>1.2896</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5695</v>
+        <v>0.3308</v>
       </c>
       <c r="V18" t="n">
         <v>-0.945</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. MERINO LUQUE</t>
+          <t>A. ARCONES DURAND</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8071</v>
+        <v>1.2894</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6966</v>
+        <v>0.9073</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8895</v>
+        <v>0.3821</v>
       </c>
       <c r="G19" t="n">
-        <v>0.402</v>
+        <v>0.8278</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0702</v>
+        <v>-1.9586</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3318</v>
+        <v>2.7864</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8245</v>
+        <v>0.8159</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7309</v>
+        <v>-0.6877</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0936</v>
+        <v>1.5036</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4225</v>
+        <v>0.0119</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.6607</v>
+        <v>-1.2708</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2381</v>
+        <v>1.2827</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>0.961</v>
+        <v>1.1646</v>
       </c>
       <c r="T19" t="n">
-        <v>0.725</v>
+        <v>1.0179</v>
       </c>
       <c r="U19" t="n">
-        <v>0.236</v>
+        <v>0.1467</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3386</v>
+        <v>0.444</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.1642</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2724</v>
+        <v>0.2799</v>
       </c>
       <c r="G20" t="n">
         <v>0.2143</v>
@@ -2014,13 +2014,13 @@
         <v>1.8529</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1244</v>
+        <v>0.2298</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4414</v>
+        <v>-0.3435</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5658</v>
+        <v>0.5733</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ARCONES DURAND</t>
+          <t>R. MERINO LUQUE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2116</v>
+        <v>0.3908</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.07199999999999999</v>
+        <v>1.3049</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2836</v>
+        <v>-0.9141</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8278</v>
+        <v>0.402</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9586</v>
+        <v>0.0702</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7864</v>
+        <v>0.3318</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8159</v>
+        <v>2.8245</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6877</v>
+        <v>2.7309</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5036</v>
+        <v>0.0936</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0119</v>
+        <v>-2.4225</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2708</v>
+        <v>-2.6607</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2827</v>
+        <v>0.2381</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4823</v>
+        <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0868</v>
+        <v>0.5447</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0386</v>
+        <v>0.3333</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0482</v>
+        <v>0.2114</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2397</v>
+        <v>-2.8585</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0159</v>
+        <v>-0.4322</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2239</v>
+        <v>-2.4262</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5018</v>
+        <v>-2.7412</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2115</v>
+        <v>-2.4263</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2903</v>
+        <v>-0.3149</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3781</v>
+        <v>0.0639</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1503</v>
+        <v>0.571</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5284</v>
+        <v>-0.5071</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1237</v>
+        <v>-2.8051</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3618</v>
+        <v>-2.9973</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2381</v>
+        <v>0.1922</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7411</v>
+        <v>1.8529</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3738</v>
+        <v>0.2151</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2151</v>
+        <v>0.4303</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1587</v>
+        <v>-0.2151</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3612</v>
+        <v>-3.2638</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6074</v>
+        <v>-2.1138</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7538</v>
+        <v>-1.15</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7412</v>
+        <v>-2.5018</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4263</v>
+        <v>-2.2115</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3149</v>
+        <v>-0.2903</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0639</v>
+        <v>-0.3781</v>
       </c>
       <c r="K23" t="n">
-        <v>0.571</v>
+        <v>0.1503</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5071</v>
+        <v>-0.5284</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8051</v>
+        <v>-2.1237</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.9973</v>
+        <v>-2.3618</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1922</v>
+        <v>0.2381</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2876</v>
+        <v>0.3498</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7449</v>
+        <v>0.1172</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5427</v>
+        <v>0.2325</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9141</v>
+        <v>-4.5149</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4634</v>
+        <v>-3.0717</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4507</v>
+        <v>-1.4433</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3149</v>
@@ -2326,13 +2326,13 @@
         <v>2.4087</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2674</v>
+        <v>0.1318</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6392</v>
+        <v>-0.2474</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3718</v>
+        <v>0.3793</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8877</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.540500000000002</v>
+        <v>5.1934</v>
       </c>
       <c r="E25" t="n">
         <v>9.2661</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.7256</v>
+        <v>-4.0726</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.225000000000002</v>
+        <v>-1.225000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>-9.7493</v>
@@ -2380,7 +2380,7 @@
         <v>12.364</v>
       </c>
       <c r="K25" t="n">
-        <v>9.255600000000001</v>
+        <v>9.255599999999999</v>
       </c>
       <c r="L25" t="n">
         <v>3.1083</v>
@@ -2404,13 +2404,13 @@
         <v>14.8229</v>
       </c>
       <c r="S25" t="n">
-        <v>6.466299999999999</v>
+        <v>7.119300000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>5.502800000000001</v>
+        <v>5.5029</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9636000000000001</v>
+        <v>1.6166</v>
       </c>
       <c r="V25" t="n">
         <v>-4.4066</v>
